--- a/reports/ai_readiness_2026-W24.xlsx
+++ b/reports/ai_readiness_2026-W24.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-08 11:31 UTC</t>
+          <t>Generated: 2026-06-08 16:47 UTC</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41.5</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="7">
@@ -744,36 +744,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timeout</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Timeout</t>
-        </is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Timeout</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" t="n">
+        <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -1044,7 +1038,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-08 11:31 UTC</t>
+          <t>Generated: 2026-06-08 16:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1161,10 +1155,10 @@
         <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D10" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
